--- a/bin/Debug/导出配置.xlsx
+++ b/bin/Debug/导出配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="14725"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>配置表目录</t>
   </si>
@@ -40,7 +40,13 @@
     <t>配置表导出路径</t>
   </si>
   <si>
-    <t>..\..\JsonData|json</t>
+    <t>..\..\JsonData\Json</t>
+  </si>
+  <si>
+    <t>CS导出路径</t>
+  </si>
+  <si>
+    <t>..\..\JsonData\Cs</t>
   </si>
 </sst>
 </file>
@@ -971,11 +977,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="29.25" customWidth="1"/>
-    <col min="2" max="2" width="46.25" customWidth="1"/>
+    <col min="1" max="1" width="29.2522522522523" customWidth="1"/>
+    <col min="2" max="2" width="46.2522522522523" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -994,6 +1000,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" customFormat="1" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1005,7 +1019,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1017,7 +1031,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/bin/Debug/导出配置.xlsx
+++ b/bin/Debug/导出配置.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>配置表目录</t>
   </si>
@@ -37,10 +37,16 @@
     <t>..\..\数据表</t>
   </si>
   <si>
-    <t>配置表导出路径</t>
+    <t>配置表导出路径1</t>
   </si>
   <si>
     <t>..\..\JsonData\Json</t>
+  </si>
+  <si>
+    <t>配置表导出路径2</t>
+  </si>
+  <si>
+    <t>..\..\JsonData\Byte</t>
   </si>
   <si>
     <t>CS导出路径</t>
@@ -977,8 +983,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="29.2522522522523" customWidth="1"/>
     <col min="2" max="2" width="46.2522522522523" customWidth="1"/>
@@ -1006,6 +1012,14 @@
       </c>
       <c r="B3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
